--- a/gear.xlsx
+++ b/gear.xlsx
@@ -22,49 +22,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="151">
   <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subcategory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dimensions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due Back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Photos</t>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subcategory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos</t>
   </si>
   <si>
     <t xml:space="preserve">Bike</t>
@@ -487,6 +487,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -507,6 +508,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -551,16 +553,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -691,1467 +697,1467 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="L3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="L3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="L4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="L4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="1" t="s">
+      <c r="L9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="1" t="s">
+      <c r="L10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="1" t="s">
+      <c r="L11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="1" t="s">
+      <c r="L12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="3"/>
+      <c r="N12" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="1" t="s">
+      <c r="L13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="H14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="1" t="s">
+      <c r="L14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="H15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="1" t="s">
+      <c r="L15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="1" t="s">
+      <c r="L16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="H17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="C18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="1" t="s">
+      <c r="L18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="L19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="1" t="s">
+      <c r="I19" s="3"/>
+      <c r="L19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="L20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="1" t="s">
+      <c r="I20" s="3"/>
+      <c r="L20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="C21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="L21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="L21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="1" t="s">
+      <c r="L22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="N22" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="C23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="H23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="1" t="s">
+      <c r="L23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="C24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1" t="s">
+      <c r="M24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1" t="s">
+      <c r="M25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="H26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="H27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="H28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="C29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="H29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="L29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="H30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1" t="s">
+      <c r="M30" s="2"/>
+      <c r="N30" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="L31" s="1" t="s">
+      <c r="I31" s="3"/>
+      <c r="L31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="1" t="s">
+      <c r="M31" s="3"/>
+      <c r="N31" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="1" t="s">
+      <c r="H32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="1" t="s">
+      <c r="L32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="H33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="1" t="s">
+      <c r="L33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="H34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1" t="s">
+      <c r="M34" s="2"/>
+      <c r="N34" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="H35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1" t="s">
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="C36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" s="1" t="s">
+      <c r="H36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M36" s="2"/>
-      <c r="N36" s="1" t="s">
+      <c r="M36" s="3"/>
+      <c r="N36" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="C37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="H37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="L37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M37" s="2"/>
-      <c r="N37" s="1" t="s">
+      <c r="M37" s="3"/>
+      <c r="N37" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="2"/>
-      <c r="L38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="2"/>
-      <c r="N38" s="1" t="s">
+      <c r="H38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="L38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="L39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
+      <c r="H39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="L39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="L40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
+      <c r="I40" s="3"/>
+      <c r="L40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I41" s="2"/>
-      <c r="L41" s="1" t="s">
+      <c r="I41" s="3"/>
+      <c r="L41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="L42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M42" s="2"/>
-      <c r="N42" s="1" t="s">
+      <c r="H42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="L42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="L43" s="1" t="s">
+      <c r="H43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="L43" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1" t="s">
+      <c r="M43" s="2"/>
+      <c r="N43" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I44" s="2"/>
-      <c r="L44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+      <c r="I44" s="3"/>
+      <c r="L44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I45" s="2"/>
-      <c r="L45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
+      <c r="I45" s="3"/>
+      <c r="L45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I46" s="2"/>
-      <c r="L46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+      <c r="I46" s="3"/>
+      <c r="L46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="L47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
+      <c r="I47" s="3"/>
+      <c r="L47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I48" s="2"/>
-      <c r="L48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
+      <c r="I48" s="3"/>
+      <c r="L48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I49" s="2"/>
-      <c r="L49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="1" t="s">
+      <c r="I49" s="3"/>
+      <c r="L49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I50" s="2"/>
-      <c r="L50" s="1" t="s">
+      <c r="I50" s="3"/>
+      <c r="L50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I51" s="2"/>
-      <c r="L51" s="1" t="s">
+      <c r="I51" s="3"/>
+      <c r="L51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
